--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202606/Currency_P&L_20260609.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202606/Currency_P&L_20260609.xlsx
@@ -541,31 +541,31 @@
         <v>46181</v>
       </c>
       <c r="B5">
-        <v>92818575.01000001</v>
+        <v>93791423.37</v>
       </c>
       <c r="C5">
-        <v>-33357.75</v>
+        <v>-150462.36</v>
       </c>
       <c r="D5">
-        <v>-0.000359</v>
+        <v>-0.001621</v>
       </c>
       <c r="E5">
-        <v>-46905.5</v>
+        <v>-41730.13</v>
       </c>
       <c r="F5">
-        <v>-0.000505</v>
+        <v>-0.00045</v>
       </c>
       <c r="G5">
-        <v>-36309.27</v>
+        <v>-89719.28</v>
       </c>
       <c r="H5">
-        <v>-0.000391</v>
+        <v>-0.000967</v>
       </c>
       <c r="I5">
-        <v>-5638165.64</v>
+        <v>1287767.41</v>
       </c>
       <c r="J5">
-        <v>-0.060744</v>
+        <v>0.013874</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -579,25 +579,25 @@
         <v>-53387.31</v>
       </c>
       <c r="D6">
-        <v>-0.000575</v>
+        <v>-0.000569</v>
       </c>
       <c r="E6">
         <v>26028.85</v>
       </c>
       <c r="F6">
-        <v>0.00028</v>
+        <v>0.000278</v>
       </c>
       <c r="G6">
         <v>90318.94</v>
       </c>
       <c r="H6">
-        <v>0.000973</v>
+        <v>0.000963</v>
       </c>
       <c r="I6">
         <v>-686562.8</v>
       </c>
       <c r="J6">
-        <v>-0.007397</v>
+        <v>-0.00732</v>
       </c>
     </row>
   </sheetData>
